--- a/public/exports-60-250/29189633.xlsx
+++ b/public/exports-60-250/29189633.xlsx
@@ -6214,12 +6214,12 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311365263</t>
+          <t xml:space="preserve">311365262</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -6289,12 +6289,12 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311365266</t>
+          <t xml:space="preserve">311365267</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366605</t>
+          <t xml:space="preserve">311366603</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
